--- a/data/seed/portfolio/L-2025-1184/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-1184/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,42 +535,42 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>12481000</v>
+        <v>6534000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Nihol Farm Savdo XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>205432993</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000430624406001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №120/26 от 01.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6946</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27981000</v>
+        <v>22034000</v>
       </c>
     </row>
     <row r="9">
@@ -580,138 +580,143 @@
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>3958000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>8591000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Yangi Hayot Moy XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>387188937</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000568867576001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №174/26 от 02.07.2026</t>
+          <t>Предоплата за материалы по дог. №86/26</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>31939000</v>
+        <v>13443000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>4409000</v>
+        <v>7256000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5910 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3980</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36348000</v>
+        <v>20699000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>14531000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>7171000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №1444</t>
+          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21817000</v>
+        <v>27870000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>72925000</v>
+        <v>4158000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -721,37 +726,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №100/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №153/26</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-51108000</v>
+        <v>23712000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>8947000</v>
+        <v>1731000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -761,117 +766,112 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2238 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №4356 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-42161000</v>
+        <v>25443000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>5818000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>1668000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olmaliq Un Mahsulotlari MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>390256500</t>
+          <t>277600485</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000130973841001</t>
+          <t>20208000938186521001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №28/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №211/26, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-47979000</v>
+        <v>27111000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1300000</v>
+        <v>8591000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>357573728</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000268446330001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №90/20</t>
+          <t>Tovarlar uchun to'lov h/f №3477</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-49279000</v>
+        <v>18520000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8564000</v>
+        <v>14531000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>264054329</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -881,37 +881,37 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №122/26</t>
+          <t>IYUN OYI UCHUN ISH HAQI, REESTR №7315</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-57843000</v>
+        <v>3989000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>11174000</v>
+        <v>16131000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -921,37 +921,37 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3768</t>
+          <t>Оплата за упаковочные материалы, с/ф №6686</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-69017000</v>
+        <v>-12142000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>7801000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>21984000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -961,197 +961,197 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3948 за поставленный товар</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №2858</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-61216000</v>
+        <v>-34126000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>45201000</v>
+        <v>6080000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9040 13.07.2026, QQS bilan</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8613</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-16015000</v>
+        <v>-28046000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>10973000</v>
+        <v>1267000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №72/26, НДС 12%</t>
+          <t>Shartnoma №267/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-5042000</v>
+        <v>-26779000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>2128000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bekobod Qurilish MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>310244257</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000890407959001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6978 за поставленный товар</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №18/22</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-2914000</v>
+        <v>-28079000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>2326000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>27020000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>313498577</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000462929469001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2600 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №238/26</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-588000</v>
+        <v>-55099000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>10069000</v>
+        <v>10192000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,392 +1161,397 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №118/26, НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №229/26, QQS 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9481000</v>
+        <v>-44907000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>4197000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16307000284956168417</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №277/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3981000</v>
+        <v>-40710000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>9441000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>1407000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olmaliq Un Mahsulotlari MChJ</t>
+          <t>Nukus Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>390256500</t>
+          <t>283442139</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000130973841001</t>
+          <t>20208000207537412001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №121/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №219/26, QQS 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-5460000</v>
+        <v>-39303000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>2539000</v>
+        <v>3244000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №19/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №93/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-2921000</v>
+        <v>-36059000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>1981000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>2915000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>-4902000</v>
+        <v>-33144000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1981000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>1964000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartnoma №112/26, QQS 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-6883000</v>
+        <v>-31180000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>2618000</v>
+        <v>4385000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №295/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4133</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-4265000</v>
+        <v>-26795000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>8669000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>4035000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farg'ona Logistik XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>227332498</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000853566483001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №123/26 от 17.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6840</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-12934000</v>
+        <v>-22760000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>11060000</v>
+        <v>3229000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №211/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №197/26, НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>-1874000</v>
+        <v>-19531000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>2017000</v>
+        <v>1339000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Nukus Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>283442139</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000207537412001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1200</t>
+          <t>Предоплата за товар по договору №101/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>143000</v>
+        <v>-18192000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>9881000</v>
+        <v>1298000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,237 +1561,232 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №116/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №213/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10024000</v>
+        <v>-16894000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46226</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>2979000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>9894000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №3/26 ОТ 23.07.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №144/26, QQS bilan</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13003000</v>
+        <v>-26788000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>2618000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335459974</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000153086692001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Предоплата за товар по договору №291/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10907000</v>
+        <v>-24170000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46227</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>6102000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>5359000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №20/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №175/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17009000</v>
+        <v>-29529000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>16865000</v>
+        <v>1981000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barakali Sut Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>223303148</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000028358608001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №79/26</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>144000</v>
+        <v>-31510000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>3959000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>1981000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8698 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4103000</v>
+        <v>-33491000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>2636000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>237330749</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>16307000284956168417</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,157 +1796,157 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №255/26 ОТ 27.07.2026</t>
+          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6739000</v>
+        <v>-38991000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>813000</v>
+        <v>6465000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000869428102001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №37/26</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5926000</v>
+        <v>-45456000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>20378000</v>
+        <v>7325000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №243/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №74/26</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>-14452000</v>
+        <v>-52781000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46231</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>5171000</v>
+        <v>2351000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Saodat Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>294172130</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000777348981001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №66/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №658</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>-9281000</v>
+        <v>-50430000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>2523000</v>
+        <v>3798000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1956,152 +1956,157 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №224/26 от 29.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №119/26, QQS 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>-6758000</v>
+        <v>-46632000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>6904000</v>
+        <v>2518000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №65/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №5699 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>146000</v>
+        <v>-44114000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>5744000</v>
+        <v>2026000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8793 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5890000</v>
+        <v>-42088000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>2210000</v>
+        <v>1743000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №203/26 bo'yicha oldindan to'lov</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №5733 20.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8100000</v>
+        <v>-40345000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46234</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>1421000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2111,37 +2116,37 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2472</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7800000</v>
+        <v>-38924000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>7018000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>4457000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2151,672 +2156,672 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shartnoma №251/26 bo'yicha oldindan to'lov</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №201/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14818000</v>
+        <v>-43381000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>5149000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>8256000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №47/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №285/26, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19967000</v>
+        <v>-51637000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>1637000</v>
+        <v>8041000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №60/26, НДС 12%</t>
+          <t>Shartnoma №158/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21604000</v>
+        <v>-43596000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>1396000</v>
+        <v>2097000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6266 за поставленный товар</t>
+          <t>Оплатапо счет-фактуре №7072 за поставленный товар</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>23000000</v>
+        <v>-41499000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>1251000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>2078000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №202/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №205/26, QQS 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21749000</v>
+        <v>-39421000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46238</v>
+        <v>46224</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>1168000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>2261000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №139/26, НДС 12%</t>
+          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮНЬ</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22917000</v>
+        <v>-41682000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>15064000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>40298000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9422</t>
+          <t>Shartnoma №100/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7853000</v>
+        <v>-1384000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>1574000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>813000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000832193729001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №143/26, QQS 12%</t>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9427000</v>
+        <v>-2197000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>1063000</v>
+        <v>17225000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №544 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8464</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10490000</v>
+        <v>15028000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>995000</v>
+        <v>10912000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shartnoma №101/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4872</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11485000</v>
+        <v>25940000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>1348000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>8253000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>357573728</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000268446330001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №90/20</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5788</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10137000</v>
+        <v>34193000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46245</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>4305000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>5785000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Nukus Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>283442139</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000207537412001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3656</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6727 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5832000</v>
+        <v>39978000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46245</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>9742000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>4368000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7413</t>
+          <t>Оплата за продукцию по договору №269/26, НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-3910000</v>
+        <v>44346000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46245</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>38460000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>1433000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №285/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №566 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>-42370000</v>
+        <v>45779000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46246</v>
+        <v>46232</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>3690000</v>
+        <v>1538000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Nukus Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>283442139</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000207537412001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5217 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №294/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-38680000</v>
+        <v>47317000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46246</v>
+        <v>46233</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>1232000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>7403000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1518 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №278/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-37448000</v>
+        <v>39914000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46246</v>
+        <v>46233</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>4539000</v>
+        <v>19359000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №261/26</t>
+          <t>Tovarlar uchun to'lov h/f №4000</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-41987000</v>
+        <v>20555000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46247</v>
+        <v>46234</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>849000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>237330749</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2826,37 +2831,37 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5129</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-41138000</v>
+        <v>20255000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>792000</v>
+        <v>9702000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2866,272 +2871,272 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №165/26, НДС 12%</t>
+          <t>SHARTNOMA №194/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-40346000</v>
+        <v>29957000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>3090000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>6360000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Buxoro Dori-Darmon MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>234941721</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000057773489001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №239/26 от 14.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №15/26, QQS 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-43436000</v>
+        <v>36317000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>4736000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>27230000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Olmaliq Un Mahsulotlari MChJ</t>
+          <t>Nukus Yog' Zavodi XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>390256500</t>
+          <t>283442139</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000130973841001</t>
+          <t>20208000207537412001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №278/26</t>
+          <t>Оплата за продукцию по договору №74/26, НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-48172000</v>
+        <v>63547000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>5566000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>22539000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №234/26</t>
+          <t>Предоплата за товар по договору №147/26 от 04.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-53738000</v>
+        <v>86086000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>5500000</v>
+        <v>4886000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>16307000284956168417</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №119/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-59238000</v>
+        <v>81200000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>5919000</v>
+        <v>1566000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3285 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №166/26 от 05.08.2026</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>-53319000</v>
+        <v>82766000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>1210000</v>
+        <v>4390000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barakali Sut Mahsulotlari MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>223303148</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000028358608001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8870</t>
+          <t>Оплата за упаковочные материалы, с/ф №9932</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-54529000</v>
+        <v>78376000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>1674000</v>
+        <v>15064000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>370685308</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3141,117 +3146,117 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №82/26, QQS bilan</t>
+          <t>Iyul oyi uchun ish haqi, reestr №5246</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-56203000</v>
+        <v>63312000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>15491000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7593</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-58257000</v>
+        <v>78803000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>2054000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>1607000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №159/26, QQS 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>-60311000</v>
+        <v>80410000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>2193000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>1281000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3261,357 +3266,357 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5779</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>-62504000</v>
+        <v>81691000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46241</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2304000</v>
+        <v>1348000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Bekobod Qurilish MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>310244257</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000890407959001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №6/26 от 17.08.2026, НДС 12%</t>
+          <t>Арендная плата за август 2026 г. по договору №18/22</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>-64808000</v>
+        <v>80343000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46252</v>
+        <v>46241</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>1650000</v>
+        <v>3944000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Olmaliq Un Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Moy XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>390256500</t>
+          <t>387188937</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000130973841001</t>
+          <t>20208000568867576001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №74/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №173/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-66458000</v>
+        <v>76399000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>2422000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>3116000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>260925717</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000558368011001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7745</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8831 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-68880000</v>
+        <v>79515000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>1637000</v>
+        <v>1657000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №601 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №175/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-67243000</v>
+        <v>81172000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46254</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>4781000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>1299000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Saodat Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>294172130</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000777348981001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №9944</t>
+          <t>Оплата за продукцию по дог. №173/26, НДС 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>-72024000</v>
+        <v>82471000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46255</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>4190000</v>
+        <v>996000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Logistik XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>227332498</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000853566483001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №42/26, QQS 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>-67834000</v>
+        <v>83467000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>44637000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>3548000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shartnoma №260/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №45/26</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-23197000</v>
+        <v>79919000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>13136000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>3691000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №18/26 от 24.08.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №117/26</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-10061000</v>
+        <v>76228000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>2111000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>8324000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Yangi Hayot Moy XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>387188937</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000568867576001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,42 +3626,42 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №201/26 от 24.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №182/26, QQS bilan</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>-7950000</v>
+        <v>67904000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>1442000</v>
+        <v>13569000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona XK</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>274834421</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000972075374001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3665,33 +3670,33 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>-6508000</v>
+        <v>81473000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46258</v>
+        <v>46245</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>895000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>59095000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3701,157 +3706,157 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5258 24.08.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №201/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-5613000</v>
+        <v>22378000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>1420000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>8000000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №462</t>
+          <t>Оплата по счет-фактуре №6409 за поставленный товар</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>-7033000</v>
+        <v>30378000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>2270000</v>
+        <v>8547000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Оплата за сырье по договору №65/26 от 13.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-9303000</v>
+        <v>21831000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>56581000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>16966000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>277600485</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000938186521001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №3/26 от 24.08.2026, НДС 12%</t>
+          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>-65884000</v>
+        <v>38797000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>677000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>4928000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3861,77 +3866,72 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №177/26 от 25.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №6985</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-65207000</v>
+        <v>33869000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46260</v>
+        <v>46249</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>843000</v>
+        <v>5500000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>200933985</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000869428102001</t>
+          <t>16307000284956168417</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-66050000</v>
+        <v>28369000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>3931000</v>
+        <v>2213000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3941,357 +3941,357 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №192/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №39/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>-62119000</v>
+        <v>30582000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>3269000</v>
+        <v>1158000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4784 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №6750 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>-58850000</v>
+        <v>31740000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>1021000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>2054000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №57/26 от 27.08.2026</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>-57829000</v>
+        <v>29686000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46261</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>3771000</v>
+        <v>2054000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3844</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-61600000</v>
+        <v>27632000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46262</v>
+        <v>46252</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>3674000</v>
+        <v>4783000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona XK</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>274834421</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000972075374001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6292 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2644</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-57926000</v>
+        <v>32415000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>1886000</v>
+        <v>2645000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8284 21.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>-56040000</v>
+        <v>35060000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>68282000</v>
+        <v>1150000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Saodat Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>294172130</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000777348981001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2223</t>
+          <t>Tovar uchun to'lov, h/f №6257 21.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>12242000</v>
+        <v>36210000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>3075000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>2114000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9889 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i iyl oyi</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>15317000</v>
+        <v>34096000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>1428000</v>
+        <v>7442000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3128 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1807</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>16745000</v>
+        <v>41538000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>1411000</v>
+        <v>1230000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Farg'ona Logistik XK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>227332498</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000853566483001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4301,112 +4301,117 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №191/26 от 31.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4010 24.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>18156000</v>
+        <v>42768000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>882000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Saodat Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>294172130</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000777348981001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2693</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>17856000</v>
+        <v>43650000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>1794000</v>
+        <v>843000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000832193729001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №175/26 от 31.08.2026, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>16062000</v>
+        <v>42807000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>1804000</v>
+        <v>3875000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4416,37 +4421,37 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №18/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №119/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>14258000</v>
+        <v>38932000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3000000</v>
+        <v>40913000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4456,77 +4461,77 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8221</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №268/26</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>11258000</v>
+        <v>-1981000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46267</v>
+        <v>46259</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>4518000</v>
+        <v>2546000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №98/26 от 02.9.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2415</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>15776000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>2790000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>2457000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4536,197 +4541,197 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2632</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №197/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>12986000</v>
+        <v>3022000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>10696000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1417000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №288/26</t>
+          <t>SHARTNOMA №89/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2290000</v>
+        <v>4439000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>6579000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>11326000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Moy XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>387188937</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000568867576001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №295/26 от 04.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartn. №180/26, QQS bilan</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>8869000</v>
+        <v>-6887000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>6067000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>1100000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Buxoro Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>230314840</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000835860827001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1755</t>
+          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2802000</v>
+        <v>-5787000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>2715000</v>
+        <v>808000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3961 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5023 27.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>5517000</v>
+        <v>-4979000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>2122000</v>
+        <v>5202000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4736,72 +4741,77 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №253/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3914</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>7639000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>15771000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>4366000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Qarshi Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>335459974</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000153086692001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА АВГУСТ 2026 Г. СОГЛАСНО РЕЕСТРУ №8356</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2585</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>-8132000</v>
+        <v>4589000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>4281000</v>
+        <v>4346000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4811,157 +4821,152 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №299/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №31/26, QQS 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>-3851000</v>
+        <v>8935000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>3252000</v>
+        <v>1015000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1215 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6886</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>-599000</v>
+        <v>9950000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1411000</v>
+        <v>300000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>357573728</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000268446330001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №90/20</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>-2010000</v>
+        <v>9650000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>9567000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>11881000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Saodat Moy AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>225650001</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000097384176001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №99/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>-11577000</v>
+        <v>21531000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>9041000</v>
+        <v>9461000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4971,37 +4976,37 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №12 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №9846 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>-2536000</v>
+        <v>30992000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>3425000</v>
+        <v>9140000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5011,37 +5016,37 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №10/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №6054 01.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>889000</v>
+        <v>40132000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>2538000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>2063000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Buxoro Dori-Darmon MChJ</t>
+          <t>Qarshi Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>234941721</t>
+          <t>335459974</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000057773489001</t>
+          <t>20208000153086692001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5051,37 +5056,37 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4743</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4179</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>-1649000</v>
+        <v>42195000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>11001000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>3160000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5091,197 +5096,197 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №33/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-12650000</v>
+        <v>45355000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>25006000</v>
+        <v>2536000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №232/26 от 14.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4035</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>12356000</v>
+        <v>47891000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>7941000</v>
+        <v>853000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №199/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №665 02.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>20297000</v>
+        <v>48744000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>7002000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>19789000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1158 14.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №200/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>27299000</v>
+        <v>28955000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>3672000</v>
+        <v>3572000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Saodat Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>294172130</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000777348981001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №284/26 от 14.09.2026</t>
+          <t>Shartnoma №109/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>30971000</v>
+        <v>32527000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>3324000</v>
+        <v>1340000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5291,152 +5296,157 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №202/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5600</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>34295000</v>
+        <v>33867000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>2151000</v>
+        <v>6708000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата за транспортные услуги по дог. №184/26</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>32144000</v>
+        <v>27159000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>2151000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>3273000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА АВГУСТ 2026 Г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3198</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>29993000</v>
+        <v>30432000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>3177000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
+          <t>Nihol Farm Savdo XK</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>205432993</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>16307000284956168417</t>
+          <t>20208000430624406001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>24493000</v>
+        <v>33609000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>6298000</v>
+        <v>2463000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5446,37 +5456,37 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4149 16.09.2026, QQS bilan</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №30/26, QQS 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>30791000</v>
+        <v>36072000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>1878000</v>
+        <v>1751000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5486,157 +5496,152 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №109/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №217/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>32669000</v>
+        <v>37823000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>4474000</v>
+        <v>808000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №3/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №297/26, QQS 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>37143000</v>
+        <v>38631000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>4083000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>3202000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2155 от 17.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №1/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>41226000</v>
+        <v>35429000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46282</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>7521000</v>
+        <v>6249000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Yangi Hayot Moy XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>387188937</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000568867576001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №87/26 от 17.09.2026, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №286/26</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>33705000</v>
+        <v>29180000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46283</v>
+        <v>46272</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>2107000</v>
+        <v>15771000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>264054329</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5646,77 +5651,77 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5073</t>
+          <t>Ishhaqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>31598000</v>
+        <v>13409000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>4573000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>2458000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №14/26, QQS bilan</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6074</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>27025000</v>
+        <v>15867000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>6959000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>1009000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Namangan Mato AJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>370685308</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000508940110001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5726,77 +5731,77 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №20/26</t>
+          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>20066000</v>
+        <v>16876000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>26288000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>1411000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Bekobod Qurilish MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>310244257</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000890407959001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №209/26, НДС 12%</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartn. №18/22</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46354000</v>
+        <v>15465000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>7782000</v>
+        <v>5145000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5806,77 +5811,77 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1206</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>54136000</v>
+        <v>20610000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>7600000</v>
+        <v>2605000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №259/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9744</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>61736000</v>
+        <v>23215000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>6099000</v>
+        <v>844000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Olmaliq Qog'oz MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>215480391</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000986709941001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5886,117 +5891,117 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №223/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №29</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>67835000</v>
+        <v>24059000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1985000</v>
+        <v>6463000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Navoiy Savdo MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>260925717</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000558368011001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4761</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №109/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>65850000</v>
+        <v>17596000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>2384000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>33618000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335459974</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000153086692001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Tovar uchun to'lov, hisob-faktura №807 11.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>63466000</v>
+        <v>51214000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>6057000</v>
+        <v>3540000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,77 +6011,77 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №229/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №163/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>57409000</v>
+        <v>47674000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>57431000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>8137000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №258/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №226/26, QQS 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-22000</v>
+        <v>55811000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1791000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>12854000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Jizzax Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>263273324</t>
+          <t>373728426</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>20208000446330386001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6086,77 +6091,77 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7019 22.09.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №287/26</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1769000</v>
+        <v>42957000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>3115000</v>
+        <v>19691000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>236972169</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000305703915001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №77/26</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6501</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>-1346000</v>
+        <v>23266000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>17074000</v>
+        <v>3228000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6166,157 +6171,152 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5802 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №3463 15.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>15728000</v>
+        <v>26494000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>9394000</v>
+        <v>1627000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>289354599</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000441530866001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №754 15.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>25122000</v>
+        <v>28121000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>15125000</v>
+        <v>2151000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Buxoro Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>234941721</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000057773489001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6689</t>
+          <t>IJTIMOIY SOLIQ AVGUST 2026</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>9997000</v>
+        <v>25970000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>8662000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>2151000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ziyo Mehmonxona XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>274834421</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000972075374001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9913 за поставленный товар</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>18659000</v>
+        <v>23819000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>3757000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>263273324</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-1184)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000828535664001</t>
+          <t>16307000284956168417</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6326,37 +6326,37 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №101/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-1184 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>22416000</v>
+        <v>18319000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>882000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>3055000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bog'ishamol Non MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>333074992</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000869428102001</t>
+          <t>20208000739304798001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,37 +6366,37 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7177</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>21534000</v>
+        <v>21374000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>12906000</v>
+        <v>4357000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>266668909</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000718504702001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6406,37 +6406,37 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №164/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №9749</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>8628000</v>
+        <v>17017000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>3506000</v>
+        <v>3767000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>348039129</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000670994127001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6446,151 +6446,1191 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №936 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5247</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>12134000</v>
+        <v>20784000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>4555000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>13976000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Oydin Moy MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>264054329</t>
+          <t>277600485</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000334306244001</t>
+          <t>20208000938186521001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6889</t>
+          <t>Оплата за товар по счет-фактуре №8508 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>7579000</v>
+        <v>34760000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>7121000</v>
+        <v>12006000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kamalak Meva Eksport MChJ</t>
+          <t>Farg'ona Logistik XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>237330749</t>
+          <t>227332498</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000227393047001</t>
+          <t>20208000853566483001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №212/26 от 30.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7660</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>14700000</v>
+        <v>46766000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>6045000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №65/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>52811000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>4054000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8365</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>56865000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>2777000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №586 21.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>59642000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>2066000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7356</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>61708000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Farg'ona Logistik XK</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>227332498</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000853566483001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №231/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>63437000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>1283000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>348039129</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000670994127001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>64720000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>2419000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Уплата налога на добавленную стоимость за август</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>62301000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>24132000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>236972169</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000305703915001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'ov, shartnoma №249/26</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>38169000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>8007000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1317</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>46176000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3359</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>47592000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>2304000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>348039129</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000670994127001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>49896000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>11642000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>61538000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>2757000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>64295000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>3357000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>236972169</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000305703915001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №125/26</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>60938000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>1949000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Durdona Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>277600485</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000938186521001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №1859 25.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>62887000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>1321000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Shartnoma №106/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>64208000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>1966000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №62/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>66174000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>882000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000832193729001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>65292000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>2393000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>236972169</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000305703915001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №135/26</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>62899000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>20245000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>236972169</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000305703915001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №138/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>42654000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B179" t="n">
+        <v>271</v>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>24762000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>266668909</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000718504702001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №3286</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>17892000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>2378000</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo XK</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>266668909</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000718504702001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №8374</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>15514000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>2516000</v>
+      </c>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ziyo Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>313498577</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000462929469001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №176/26</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>12998000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B182" t="n">
+        <v>274</v>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>3597000</v>
+      </c>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>236972169</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000305703915001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №104/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>9401000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B183" t="n">
+        <v>275</v>
+      </c>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n">
+        <v>3826000</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Farg'ona Logistik XK</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>227332498</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000853566483001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №1346 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>13227000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B184" t="n">
+        <v>276</v>
+      </c>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n">
+        <v>1473000</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Non MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>333074992</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000739304798001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №4891 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>14700000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="n">
+        <v>277</v>
+      </c>
+      <c r="C185" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" t="inlineStr">
         <is>
           <t>Sarbon Moliya Bank</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Hisob-kassa xizmati uchun haq</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
         <v>14400000</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n">
-        <v>563605000</v>
-      </c>
-      <c r="D160" s="4" t="n">
-        <v>562505000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="C186" s="4" t="n">
+        <v>567222000</v>
+      </c>
+      <c r="D186" s="4" t="n">
+        <v>566122000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C187" s="4" t="n">
         <v>14400000</v>
       </c>
-      <c r="D161" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
